--- a/441-rc---tdduipatient-birthdate/ig/CodeSystem-tddui-task-input-prestation.xlsx
+++ b/441-rc---tdduipatient-birthdate/ig/CodeSystem-tddui-task-input-prestation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T15:34:05+00:00</t>
+    <t>2026-02-26T16:28:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/441-rc---tdduipatient-birthdate/ig/CodeSystem-tddui-task-input-prestation.xlsx
+++ b/441-rc---tdduipatient-birthdate/ig/CodeSystem-tddui-task-input-prestation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:28:52+00:00</t>
+    <t>2026-02-26T17:10:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
